--- a/5-聚类校正与多结局依赖（数据表）.xlsx
+++ b/5-聚类校正与多结局依赖（数据表）.xlsx
@@ -4793,12 +4793,12 @@
       </c>
       <c r="AU6" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-001（原文献自称 quasi-experimental 与班级随机分配并存）</t>
+          <t>疑问编号 001（原文献自称 quasi-experimental 与班级随机分配并存）</t>
         </is>
       </c>
       <c r="AV6" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW6" s="5" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AX6" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY6" s="5" t="inlineStr">
@@ -5056,7 +5056,7 @@
       <c r="AU7" s="5" t="inlineStr"/>
       <c r="AV7" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW7" s="5" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AX7" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY7" s="5" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="AU8" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-002（CT 分析 N 三值并存：174／153／146）</t>
+          <t>疑问编号 002（CT 分析 N 三值并存：174／153／146）</t>
         </is>
       </c>
       <c r="AV8" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW8" s="5" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AX8" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY8" s="5" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="AU9" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-003（误差 df 58／59 并存）</t>
+          <t>疑问编号 003（误差 df 58／59 并存）</t>
         </is>
       </c>
       <c r="AV9" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW9" s="5" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AX9" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY9" s="5" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AQ10" s="5" t="inlineStr">
         <is>
-          <t>（保留 A/D 短摘）并在"信息缺口或异常"补记：p.5 等待组「22 children (10 girls, 43.5%; 13 boys, 56.5%)」括号内 10＋13＝23≠22，且百分比不对应 22 人的整数拆分 → 原文自身矛盾，并列记录，本表以 22（与 47−25＝22 自洽）为准</t>
+          <t>（保留 首轮提取 短摘）并在"信息缺口或异常"补记：p.5 等待组「22 children (10 girls, 43.5%; 13 boys, 56.5%)」括号内 10＋13＝23≠22，且百分比不对应 22 人的整数拆分 → 原文自身矛盾，并列记录，本表以 22（与 47−25＝22 自洽）为准</t>
         </is>
       </c>
       <c r="AR10" s="5" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="AU10" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-004（同一 T2 单元格两套 SD）</t>
+          <t>疑问编号 004（同一 T2 单元格两套 SD）</t>
         </is>
       </c>
       <c r="AV10" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW10" s="5" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AX10" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY10" s="5" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="AU11" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-005（「approximately equal」vs 46/52）</t>
+          <t>疑问编号 005（「approximately equal」vs 46/52）</t>
         </is>
       </c>
       <c r="AV11" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW11" s="5" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AX11" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY11" s="5" t="inlineStr">
@@ -6362,7 +6362,7 @@
       <c r="AU12" s="5" t="inlineStr"/>
       <c r="AV12" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW12" s="5" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="AX12" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY12" s="5" t="inlineStr">
@@ -6620,7 +6620,7 @@
       <c r="AU13" s="5" t="inlineStr"/>
       <c r="AV13" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW13" s="5" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AX13" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY13" s="5" t="inlineStr">
@@ -6878,7 +6878,7 @@
       <c r="AU14" s="5" t="inlineStr"/>
       <c r="AV14" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW14" s="5" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="AX14" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY14" s="5" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="AU15" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-006（空间定向分析 N 142 vs Table 2 的 151／163）</t>
+          <t>疑问编号 006（空间定向分析 N 142 vs Table 2 的 151／163）</t>
         </is>
       </c>
       <c r="AV15" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW15" s="5" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="AX15" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY15" s="5" t="inlineStr">
@@ -7392,17 +7392,17 @@
       </c>
       <c r="AT16" s="5" t="inlineStr">
         <is>
-          <t>数据嵌套于 4 所干预校（对照来自其中 3 所）；班级数未报告。 证据抽取方式：逐字段回PDF文本层，值＋页码＋逐字短摘；原文矛盾一律并列记录、未择一。〔群规模是否不等＝是，逐群人数：26、84、37、166〕 B/V 另发现原文表格内部矛盾（A/D 未记）：Table 2 的 Attitudes 列逐校 24／–／31／45（合计 100）与该列 Total 91 相差 9，且含一个无数据列的孤立表头 "Number" → 并列记录，本工作包字段不受影响。</t>
+          <t>数据嵌套于 4 所干预校（对照来自其中 3 所）；班级数未报告。 证据抽取方式：逐字段回PDF文本层，值＋页码＋逐字短摘；原文矛盾一律并列记录、未择一。〔群规模是否不等＝是，逐群人数：26、84、37、166〕 复核提取 另发现原文表格内部矛盾（首轮提取 未记）：Table 2 的 Attitudes 列逐校 24／–／31／45（合计 100）与该列 Total 91 相差 9，且含一个无数据列的孤立表头 "Number" → 并列记录，本表字段不受影响。</t>
         </is>
       </c>
       <c r="AU16" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-007（对照 N：55 vs 表头 51）</t>
+          <t>疑问编号 007（对照 N：55 vs 表头 51）</t>
         </is>
       </c>
       <c r="AV16" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW16" s="5" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AX16" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY16" s="5" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>NR-原文未报告（原文未说明班级→条件分配的时点；A/D 原填"干预开始前"系由"参加编码实验室"的时点推断，按字段字典"不得由研究流程常识推断"更正）</t>
+          <t>NR-原文未报告（原文未说明班级→条件分配的时点；首轮提取 原填"干预开始前"系由"参加编码实验室"的时点推断，按字段字典"不得由研究流程常识推断"更正）</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-008（学校数单复数、随访时距、设计名称三处不一致）</t>
+          <t>疑问编号 008（学校数单复数、随访时距、设计名称三处不一致）</t>
         </is>
       </c>
       <c r="AV17" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW17" s="5" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX17" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY17" s="5" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-009（「statistical corrections」内容未说明）</t>
+          <t>疑问编号 009（「statistical corrections」内容未说明）</t>
         </is>
       </c>
       <c r="AV18" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW18" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="AX18" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY18" s="5" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="AT19" s="5" t="inlineStr">
         <is>
-          <t>既有班级为分配单位而班级数未报告；分析在个体层（增益分）。 证据抽取方式：逐字段回PDF文本层，值＋页码＋逐字短摘；原文矛盾一律并列记录、未择一。 P-W20 的结果表（Table IV—X）**无文本层（矢量轮廓绘制，非位图）**：A/D 与 B/V 均以 300dpi 渲染＋macOS Vision OCR 取值，两方独立复现同一单元格（Table VII "Total score (gain)"：t(70)＝1.7350／0.0436／d＝0.4089），可直接复核。</t>
+          <t>既有班级为分配单位而班级数未报告；分析在个体层（增益分）。 证据抽取方式：逐字段回PDF文本层，值＋页码＋逐字短摘；原文矛盾一律并列记录、未择一。 P-W20 的结果表（Table IV—X）**无文本层（矢量轮廓绘制，非位图）**：首轮提取 与 复核提取 均以 300dpi 渲染＋macOS Vision OCR 取值，两方独立复现同一单元格（Table VII "Total score (gain)"：t(70)＝1.7350／0.0436／d＝0.4089），可直接复核。</t>
         </is>
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>Q-WP2-010（个体口径与班级口径并列、班级数缺失）</t>
+          <t>疑问编号 010（个体口径与班级口径并列、班级数缺失）</t>
         </is>
       </c>
       <c r="AV19" s="5" t="inlineStr">
         <is>
-          <t>A/D</t>
+          <t>首轮提取</t>
         </is>
       </c>
       <c r="AW19" s="5" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AX19" s="5" t="inlineStr">
         <is>
-          <t>已锁定（含 PI 裁定 v2）</t>
+          <t>已锁定（含 裁定记录 v2）</t>
         </is>
       </c>
       <c r="AY19" s="5" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>W35-001（外部复核《工作包1-2-3-研究数据完整性复核-20260921》第 2 项）</t>
+          <t>W35-001（外部复核《研究数据完整性复核记录》第 2 项）</t>
         </is>
       </c>
       <c r="AV20" s="5" t="inlineStr">
@@ -9354,7 +9354,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -9369,7 +9369,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -9384,7 +9384,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -9399,7 +9399,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -9414,7 +9414,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -9429,7 +9429,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -9444,7 +9444,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -9459,7 +9459,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -9474,7 +9474,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -9489,7 +9489,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -9504,7 +9504,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -9519,7 +9519,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -9527,14 +9527,14 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DER = File.join(DIR, '信度重估-派生')</t>
+          <t>DER = File.join(DIR, '派生数据')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -9549,7 +9549,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -9560,7 +9560,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -9575,7 +9575,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
@@ -9590,7 +9590,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -9605,7 +9605,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -9620,7 +9620,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -9635,7 +9635,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -9650,7 +9650,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -9665,7 +9665,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -9680,7 +9680,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -9695,7 +9695,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -9710,7 +9710,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -9725,7 +9725,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -9740,7 +9740,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -9755,7 +9755,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -9770,7 +9770,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -9785,7 +9785,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -9800,7 +9800,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -9815,7 +9815,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -9830,7 +9830,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -9845,7 +9845,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -9860,7 +9860,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -9875,7 +9875,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -9890,7 +9890,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -9905,7 +9905,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -9920,7 +9920,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -9935,7 +9935,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -9950,7 +9950,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -9965,7 +9965,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -9980,7 +9980,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -9995,7 +9995,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -10010,7 +10010,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -10025,7 +10025,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -10040,7 +10040,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -10055,7 +10055,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
@@ -10070,7 +10070,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -10085,7 +10085,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -10100,7 +10100,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -10115,7 +10115,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -10130,7 +10130,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -10145,7 +10145,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -10160,7 +10160,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -10175,7 +10175,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -10190,7 +10190,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -10205,7 +10205,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -10220,7 +10220,7 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -10235,7 +10235,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -10250,7 +10250,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -10265,7 +10265,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -10280,7 +10280,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -10295,7 +10295,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -10310,7 +10310,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -10325,7 +10325,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -10340,7 +10340,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -10355,7 +10355,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -10370,7 +10370,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -10385,7 +10385,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -10400,7 +10400,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -10415,7 +10415,7 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -10430,7 +10430,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -10445,7 +10445,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -10456,7 +10456,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -10471,7 +10471,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -10486,7 +10486,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -10501,7 +10501,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -10516,7 +10516,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -10531,7 +10531,7 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -10546,7 +10546,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -10561,7 +10561,7 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -10576,7 +10576,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
@@ -10591,7 +10591,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -10606,7 +10606,7 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -10621,7 +10621,7 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -10636,7 +10636,7 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -10651,7 +10651,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -10666,7 +10666,7 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -10681,7 +10681,7 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -10696,7 +10696,7 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -10711,7 +10711,7 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -10726,7 +10726,7 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -10741,7 +10741,7 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -10756,7 +10756,7 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -10771,7 +10771,7 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -10786,7 +10786,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -10801,7 +10801,7 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -10816,7 +10816,7 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -10831,7 +10831,7 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -10846,7 +10846,7 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -10861,7 +10861,7 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -10876,7 +10876,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -10891,7 +10891,7 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -10902,7 +10902,7 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -10910,14 +10910,14 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t># ── v26 增补：叠加工作包3 主口径(M)的独立复核裁定（11 条重判建议）────</t>
+          <t># ── v26 增补：叠加任务3 主口径(M)的独立复核裁定（11 条重判建议）────</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -10925,14 +10925,14 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>OVR = File.join(DIR, 'v26-论文质量提升五项/03-边界记录敏感性/03-分歧与裁定/WP3-M裁定-对231行判定的更新-v1.csv')</t>
+          <t>OVR = File.join(DIR, '复核裁定-对231行判定的更新-v1.csv')</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -10947,7 +10947,7 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -10962,7 +10962,7 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -10970,14 +10970,14 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  OVRID[s8(r['效应ID']).strip] = { cat: s8(r['WP3-M裁定类别']).strip, dist: s8(r['更新后迁移距离']).strip }</t>
+          <t xml:space="preserve">  OVRID[s8(r['效应ID']).strip] = { cat: s8(r['复核裁定类别']).strip, dist: s8(r['更新后迁移距离']).strip }</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
@@ -10992,7 +10992,7 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
@@ -11007,7 +11007,7 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -11022,7 +11022,7 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -11037,7 +11037,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -11052,7 +11052,7 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
@@ -11067,7 +11067,7 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
@@ -11075,14 +11075,14 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>STDERR.puts "WP3 更新 #{OVRID.size} 条已叠加"</t>
+          <t>STDERR.puts "复核更新 #{OVRID.size} 条已叠加"</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -11097,7 +11097,7 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -11112,7 +11112,7 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -11127,7 +11127,7 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -11142,7 +11142,7 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -11157,7 +11157,7 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -11172,7 +11172,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -11187,7 +11187,7 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
@@ -11202,7 +11202,7 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
@@ -11217,7 +11217,7 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
@@ -11232,7 +11232,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
@@ -11247,7 +11247,7 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
@@ -11262,7 +11262,7 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
@@ -11273,7 +11273,7 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
@@ -11284,7 +11284,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
@@ -11299,7 +11299,7 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
@@ -11314,7 +11314,7 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
@@ -11329,7 +11329,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
@@ -11344,7 +11344,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -11359,7 +11359,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
@@ -11374,7 +11374,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
@@ -11389,7 +11389,7 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
@@ -11404,7 +11404,7 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
@@ -11419,7 +11419,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
@@ -11434,7 +11434,7 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
@@ -11449,7 +11449,7 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
@@ -11464,7 +11464,7 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
@@ -11475,7 +11475,7 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
@@ -11483,14 +11483,14 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t># ============ 工作包2：聚类校正复算 v1（PI/S） ============</t>
+          <t># ============ 任务2：聚类校正复算 v1（PI/S） ============</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
@@ -11505,7 +11505,7 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
@@ -11513,14 +11513,14 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>#       效应量层处置-v1.csv、v26 工作包2 锁定参数表</t>
+          <t>#       效应量层处置-v1.csv、v26 任务2 锁定参数表</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
@@ -11528,14 +11528,14 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t># 依据：聚类校正分析方案（v1，由草案冻结）、ICC来源与优先序手册-v1.md</t>
+          <t># 依据：聚类校正分析方案、ICC 来源与优先序手册</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
@@ -11543,14 +11543,14 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>WB2 = File.join(DIR, 'v26-论文质量提升五项/02-班级设计与聚类校正')</t>
+          <t>WB2 = File.join(DIR, '班级设计参数')</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
@@ -11565,7 +11565,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
@@ -11576,7 +11576,7 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
@@ -11591,7 +11591,7 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
@@ -11606,7 +11606,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
@@ -11621,7 +11621,7 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
@@ -11636,7 +11636,7 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
@@ -11647,7 +11647,7 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
@@ -11662,7 +11662,7 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -11677,7 +11677,7 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -11692,7 +11692,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -11707,7 +11707,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -11722,7 +11722,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -11737,7 +11737,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -11752,7 +11752,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -11767,7 +11767,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -11782,7 +11782,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -11797,7 +11797,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -11812,7 +11812,7 @@
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -11827,7 +11827,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -11842,7 +11842,7 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -11853,7 +11853,7 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -11868,7 +11868,7 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -11883,7 +11883,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -11898,7 +11898,7 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -11913,7 +11913,7 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -11928,7 +11928,7 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -11943,7 +11943,7 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
@@ -11958,7 +11958,7 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
@@ -11973,7 +11973,7 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
@@ -11984,7 +11984,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
@@ -11999,7 +11999,7 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
@@ -12014,7 +12014,7 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
@@ -12029,7 +12029,7 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
@@ -12044,7 +12044,7 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
@@ -12059,7 +12059,7 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
@@ -12074,7 +12074,7 @@
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
@@ -12089,7 +12089,7 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
@@ -12104,7 +12104,7 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
@@ -12119,7 +12119,7 @@
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
@@ -12134,7 +12134,7 @@
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
@@ -12149,7 +12149,7 @@
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
@@ -12164,7 +12164,7 @@
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
@@ -12175,7 +12175,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
@@ -12190,7 +12190,7 @@
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
@@ -12205,7 +12205,7 @@
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
@@ -12216,7 +12216,7 @@
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
@@ -12231,7 +12231,7 @@
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
@@ -12246,7 +12246,7 @@
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
@@ -12261,7 +12261,7 @@
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
@@ -12276,7 +12276,7 @@
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
@@ -12291,7 +12291,7 @@
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
@@ -12306,7 +12306,7 @@
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
@@ -12317,7 +12317,7 @@
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
@@ -12332,7 +12332,7 @@
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
@@ -12347,7 +12347,7 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
@@ -12355,14 +12355,14 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    '乙口径（22 条／9 研究，含 WP3 重判）' =&gt; sub(base, '乙'),</t>
+          <t xml:space="preserve">    '乙口径（22 条／9 研究，含 重判后）' =&gt; sub(base, '乙'),</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
@@ -12370,14 +12370,14 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    '丙口径（35 条／12 研究，含 WP3 重判）' =&gt; sub(base, '丙') }</t>
+          <t xml:space="preserve">    '丙口径（35 条／12 研究，含 重判后）' =&gt; sub(base, '丙') }</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
@@ -12392,7 +12392,7 @@
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
@@ -12403,7 +12403,7 @@
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
@@ -12414,7 +12414,7 @@
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
@@ -12422,14 +12422,14 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t># ── 评审补充：M2 覆盖面与全池统一膨胀；M5 资格调节检验 ─────────────</t>
+          <t># ── 设计效应覆盖面与全池统一膨胀；资格调节检验 ─────────────</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
@@ -12444,7 +12444,7 @@
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
@@ -12459,7 +12459,7 @@
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
@@ -12474,7 +12474,7 @@
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -12489,7 +12489,7 @@
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -12504,7 +12504,7 @@
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -12519,7 +12519,7 @@
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -12527,14 +12527,14 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>puts '【M2】设计效应（DE）膨胀覆盖面'</t>
+          <t>puts '设计效应（DE）膨胀覆盖面'</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -12549,7 +12549,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -12557,14 +12557,14 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>puts format('  WP2 参数表登记记录 %d 条；其中群层分配且群规模可得 → 实际膨胀的效应 ID %d 个（来自 %d 项研究）',</t>
+          <t>puts format('  参数表登记记录 %d 条；其中群层分配且群规模可得 → 实际膨胀的效应 ID %d 个（来自 %d 项研究）',</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -12579,7 +12579,7 @@
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -12587,14 +12587,14 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">              CSV.read(File.join(DIR, 'v26-论文质量提升五项/02-班级设计与聚类校正/班级设计参数-锁定-v2.csv'), headers: true, encoding: 'bom|utf-8').select { |r| s8(r['适用效应ID列表']).include?(k) }.map { |r| s8(r['研究ID']) }.first }.compact.uniq.size)</t>
+          <t xml:space="preserve">              CSV.read(File.join(DIR, '班级设计参数/班级设计参数-锁定-v2.csv'), headers: true, encoding: 'bom|utf-8').select { |r| s8(r['适用效应ID列表']).include?(k) }.map { |r| s8(r['研究ID']) }.first }.compact.uniq.size)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -12609,7 +12609,7 @@
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -12624,7 +12624,7 @@
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -12635,7 +12635,7 @@
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -12650,7 +12650,7 @@
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -12665,7 +12665,7 @@
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -12680,7 +12680,7 @@
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -12695,7 +12695,7 @@
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
@@ -12710,7 +12710,7 @@
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
@@ -12725,7 +12725,7 @@
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
@@ -12740,7 +12740,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
@@ -12755,7 +12755,7 @@
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
@@ -12770,7 +12770,7 @@
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
@@ -12785,7 +12785,7 @@
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
@@ -12800,7 +12800,7 @@
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
@@ -12815,7 +12815,7 @@
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
@@ -12830,7 +12830,7 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
@@ -12845,7 +12845,7 @@
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
@@ -12860,7 +12860,7 @@
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
@@ -12875,7 +12875,7 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
@@ -12890,7 +12890,7 @@
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
@@ -12905,7 +12905,7 @@
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
@@ -12920,7 +12920,7 @@
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
@@ -12935,7 +12935,7 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
@@ -12950,7 +12950,7 @@
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
@@ -12965,7 +12965,7 @@
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
@@ -12980,7 +12980,7 @@
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
@@ -12995,7 +12995,7 @@
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
@@ -13003,14 +13003,14 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>puts '【M5】资格调节检验（三级元回归，C 为参照）'</t>
+          <t>puts '资格调节检验（三级元回归，C 为参照）'</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
@@ -13025,7 +13025,7 @@
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
@@ -13040,7 +13040,7 @@
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
@@ -13055,7 +13055,7 @@
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
@@ -13070,7 +13070,7 @@
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -13085,7 +13085,7 @@
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
@@ -13100,7 +13100,7 @@
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
@@ -13115,7 +13115,7 @@
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
@@ -13130,7 +13130,7 @@
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
@@ -13145,7 +13145,7 @@
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
@@ -13156,7 +13156,7 @@
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
@@ -13171,7 +13171,7 @@
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
@@ -13186,7 +13186,7 @@
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -13201,7 +13201,7 @@
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
@@ -13216,7 +13216,7 @@
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
@@ -13231,7 +13231,7 @@
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
@@ -13246,7 +13246,7 @@
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
@@ -13261,7 +13261,7 @@
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
@@ -13276,7 +13276,7 @@
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -13291,7 +13291,7 @@
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -13306,7 +13306,7 @@
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -13321,7 +13321,7 @@
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -13336,7 +13336,7 @@
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -13351,7 +13351,7 @@
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -13366,7 +13366,7 @@
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -13381,7 +13381,7 @@
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -13396,7 +13396,7 @@
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -13411,7 +13411,7 @@
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -13426,7 +13426,7 @@
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -13441,7 +13441,7 @@
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -13456,7 +13456,7 @@
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -13471,7 +13471,7 @@
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -13486,7 +13486,7 @@
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>评审补充-聚类与调节-v1.rb</t>
+          <t>聚类与调节检验.rb</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -13501,7 +13501,7 @@
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -13516,7 +13516,7 @@
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -13531,7 +13531,7 @@
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -13546,7 +13546,7 @@
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -13561,7 +13561,7 @@
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -13576,7 +13576,7 @@
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -13591,7 +13591,7 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -13606,7 +13606,7 @@
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -13621,7 +13621,7 @@
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -13636,7 +13636,7 @@
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -13651,7 +13651,7 @@
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -13666,7 +13666,7 @@
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -13674,14 +13674,14 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>DER = File.join(DIR, '信度重估-派生')</t>
+          <t>DER = File.join(DIR, '派生数据')</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -13696,7 +13696,7 @@
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -13707,7 +13707,7 @@
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -13722,7 +13722,7 @@
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
@@ -13737,7 +13737,7 @@
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
@@ -13752,7 +13752,7 @@
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
@@ -13767,7 +13767,7 @@
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
@@ -13782,7 +13782,7 @@
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
@@ -13797,7 +13797,7 @@
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
@@ -13812,7 +13812,7 @@
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
@@ -13827,7 +13827,7 @@
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
@@ -13842,7 +13842,7 @@
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
@@ -13857,7 +13857,7 @@
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
@@ -13872,7 +13872,7 @@
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
@@ -13887,7 +13887,7 @@
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
@@ -13902,7 +13902,7 @@
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
@@ -13917,7 +13917,7 @@
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
@@ -13932,7 +13932,7 @@
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
@@ -13947,7 +13947,7 @@
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -13962,7 +13962,7 @@
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -13977,7 +13977,7 @@
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -13992,7 +13992,7 @@
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
@@ -14007,7 +14007,7 @@
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
@@ -14022,7 +14022,7 @@
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
@@ -14037,7 +14037,7 @@
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
@@ -14052,7 +14052,7 @@
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
@@ -14067,7 +14067,7 @@
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
@@ -14082,7 +14082,7 @@
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B326" s="5" t="n">
@@ -14097,7 +14097,7 @@
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B327" s="5" t="n">
@@ -14112,7 +14112,7 @@
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B328" s="5" t="n">
@@ -14127,7 +14127,7 @@
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B329" s="5" t="n">
@@ -14142,7 +14142,7 @@
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B330" s="5" t="n">
@@ -14157,7 +14157,7 @@
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B331" s="5" t="n">
@@ -14172,7 +14172,7 @@
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B332" s="5" t="n">
@@ -14187,7 +14187,7 @@
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B333" s="5" t="n">
@@ -14202,7 +14202,7 @@
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B334" s="5" t="n">
@@ -14217,7 +14217,7 @@
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B335" s="5" t="n">
@@ -14232,7 +14232,7 @@
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B336" s="5" t="n">
@@ -14247,7 +14247,7 @@
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B337" s="5" t="n">
@@ -14262,7 +14262,7 @@
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B338" s="5" t="n">
@@ -14277,7 +14277,7 @@
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B339" s="5" t="n">
@@ -14292,7 +14292,7 @@
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B340" s="5" t="n">
@@ -14307,7 +14307,7 @@
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B341" s="5" t="n">
@@ -14322,7 +14322,7 @@
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B342" s="5" t="n">
@@ -14337,7 +14337,7 @@
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B343" s="5" t="n">
@@ -14352,7 +14352,7 @@
     <row r="344">
       <c r="A344" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B344" s="5" t="n">
@@ -14367,7 +14367,7 @@
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B345" s="5" t="n">
@@ -14382,7 +14382,7 @@
     <row r="346">
       <c r="A346" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B346" s="5" t="n">
@@ -14397,7 +14397,7 @@
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B347" s="5" t="n">
@@ -14412,7 +14412,7 @@
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B348" s="5" t="n">
@@ -14427,7 +14427,7 @@
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B349" s="5" t="n">
@@ -14442,7 +14442,7 @@
     <row r="350">
       <c r="A350" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B350" s="5" t="n">
@@ -14457,7 +14457,7 @@
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B351" s="5" t="n">
@@ -14472,7 +14472,7 @@
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B352" s="5" t="n">
@@ -14487,7 +14487,7 @@
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B353" s="5" t="n">
@@ -14502,7 +14502,7 @@
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B354" s="5" t="n">
@@ -14517,7 +14517,7 @@
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B355" s="5" t="n">
@@ -14532,7 +14532,7 @@
     <row r="356">
       <c r="A356" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B356" s="5" t="n">
@@ -14547,7 +14547,7 @@
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B357" s="5" t="n">
@@ -14562,7 +14562,7 @@
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B358" s="5" t="n">
@@ -14577,7 +14577,7 @@
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B359" s="5" t="n">
@@ -14592,7 +14592,7 @@
     <row r="360">
       <c r="A360" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B360" s="5" t="n">
@@ -14603,7 +14603,7 @@
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B361" s="5" t="n">
@@ -14618,7 +14618,7 @@
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B362" s="5" t="n">
@@ -14633,7 +14633,7 @@
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B363" s="5" t="n">
@@ -14648,7 +14648,7 @@
     <row r="364">
       <c r="A364" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B364" s="5" t="n">
@@ -14663,7 +14663,7 @@
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B365" s="5" t="n">
@@ -14678,7 +14678,7 @@
     <row r="366">
       <c r="A366" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B366" s="5" t="n">
@@ -14693,7 +14693,7 @@
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B367" s="5" t="n">
@@ -14708,7 +14708,7 @@
     <row r="368">
       <c r="A368" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B368" s="5" t="n">
@@ -14723,7 +14723,7 @@
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B369" s="5" t="n">
@@ -14738,7 +14738,7 @@
     <row r="370">
       <c r="A370" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B370" s="5" t="n">
@@ -14753,7 +14753,7 @@
     <row r="371">
       <c r="A371" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B371" s="5" t="n">
@@ -14768,7 +14768,7 @@
     <row r="372">
       <c r="A372" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B372" s="5" t="n">
@@ -14783,7 +14783,7 @@
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B373" s="5" t="n">
@@ -14798,7 +14798,7 @@
     <row r="374">
       <c r="A374" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B374" s="5" t="n">
@@ -14813,7 +14813,7 @@
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B375" s="5" t="n">
@@ -14828,7 +14828,7 @@
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B376" s="5" t="n">
@@ -14843,7 +14843,7 @@
     <row r="377">
       <c r="A377" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B377" s="5" t="n">
@@ -14858,7 +14858,7 @@
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B378" s="5" t="n">
@@ -14873,7 +14873,7 @@
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B379" s="5" t="n">
@@ -14888,7 +14888,7 @@
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B380" s="5" t="n">
@@ -14903,7 +14903,7 @@
     <row r="381">
       <c r="A381" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B381" s="5" t="n">
@@ -14918,7 +14918,7 @@
     <row r="382">
       <c r="A382" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B382" s="5" t="n">
@@ -14933,7 +14933,7 @@
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B383" s="5" t="n">
@@ -14948,7 +14948,7 @@
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B384" s="5" t="n">
@@ -14963,7 +14963,7 @@
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B385" s="5" t="n">
@@ -14978,7 +14978,7 @@
     <row r="386">
       <c r="A386" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B386" s="5" t="n">
@@ -14993,7 +14993,7 @@
     <row r="387">
       <c r="A387" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B387" s="5" t="n">
@@ -15008,7 +15008,7 @@
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B388" s="5" t="n">
@@ -15023,7 +15023,7 @@
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B389" s="5" t="n">
@@ -15038,7 +15038,7 @@
     <row r="390">
       <c r="A390" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B390" s="5" t="n">
@@ -15049,7 +15049,7 @@
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B391" s="5" t="n">
@@ -15057,14 +15057,14 @@
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t># ── v26 增补：叠加工作包3 主口径(M)的独立复核裁定（11 条重判建议）────</t>
+          <t># ── v26 增补：叠加任务3 主口径(M)的独立复核裁定（11 条重判建议）────</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B392" s="5" t="n">
@@ -15072,14 +15072,14 @@
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
-          <t>OVR = File.join(DIR, 'v26-论文质量提升五项/03-边界记录敏感性/03-分歧与裁定/WP3-M裁定-对231行判定的更新-v1.csv')</t>
+          <t>OVR = File.join(DIR, '复核裁定-对231行判定的更新-v1.csv')</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B393" s="5" t="n">
@@ -15094,7 +15094,7 @@
     <row r="394">
       <c r="A394" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B394" s="5" t="n">
@@ -15109,7 +15109,7 @@
     <row r="395">
       <c r="A395" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B395" s="5" t="n">
@@ -15117,14 +15117,14 @@
       </c>
       <c r="C395" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  OVRID[s8(r['效应ID']).strip] = { cat: s8(r['WP3-M裁定类别']).strip, dist: s8(r['更新后迁移距离']).strip }</t>
+          <t xml:space="preserve">  OVRID[s8(r['效应ID']).strip] = { cat: s8(r['复核裁定类别']).strip, dist: s8(r['更新后迁移距离']).strip }</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B396" s="5" t="n">
@@ -15139,7 +15139,7 @@
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B397" s="5" t="n">
@@ -15154,7 +15154,7 @@
     <row r="398">
       <c r="A398" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B398" s="5" t="n">
@@ -15169,7 +15169,7 @@
     <row r="399">
       <c r="A399" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B399" s="5" t="n">
@@ -15184,7 +15184,7 @@
     <row r="400">
       <c r="A400" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B400" s="5" t="n">
@@ -15199,7 +15199,7 @@
     <row r="401">
       <c r="A401" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B401" s="5" t="n">
@@ -15214,7 +15214,7 @@
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B402" s="5" t="n">
@@ -15222,14 +15222,14 @@
       </c>
       <c r="C402" s="5" t="inlineStr">
         <is>
-          <t>STDERR.puts "WP3 更新 #{OVRID.size} 条已叠加"</t>
+          <t>STDERR.puts "复核更新 #{OVRID.size} 条已叠加"</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B403" s="5" t="n">
@@ -15244,7 +15244,7 @@
     <row r="404">
       <c r="A404" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B404" s="5" t="n">
@@ -15259,7 +15259,7 @@
     <row r="405">
       <c r="A405" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B405" s="5" t="n">
@@ -15274,7 +15274,7 @@
     <row r="406">
       <c r="A406" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B406" s="5" t="n">
@@ -15289,7 +15289,7 @@
     <row r="407">
       <c r="A407" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B407" s="5" t="n">
@@ -15304,7 +15304,7 @@
     <row r="408">
       <c r="A408" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B408" s="5" t="n">
@@ -15319,7 +15319,7 @@
     <row r="409">
       <c r="A409" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B409" s="5" t="n">
@@ -15334,7 +15334,7 @@
     <row r="410">
       <c r="A410" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B410" s="5" t="n">
@@ -15349,7 +15349,7 @@
     <row r="411">
       <c r="A411" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B411" s="5" t="n">
@@ -15364,7 +15364,7 @@
     <row r="412">
       <c r="A412" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B412" s="5" t="n">
@@ -15379,7 +15379,7 @@
     <row r="413">
       <c r="A413" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B413" s="5" t="n">
@@ -15394,7 +15394,7 @@
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B414" s="5" t="n">
@@ -15409,7 +15409,7 @@
     <row r="415">
       <c r="A415" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B415" s="5" t="n">
@@ -15420,7 +15420,7 @@
     <row r="416">
       <c r="A416" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B416" s="5" t="n">
@@ -15431,7 +15431,7 @@
     <row r="417">
       <c r="A417" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B417" s="5" t="n">
@@ -15446,7 +15446,7 @@
     <row r="418">
       <c r="A418" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B418" s="5" t="n">
@@ -15461,7 +15461,7 @@
     <row r="419">
       <c r="A419" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B419" s="5" t="n">
@@ -15476,7 +15476,7 @@
     <row r="420">
       <c r="A420" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B420" s="5" t="n">
@@ -15491,7 +15491,7 @@
     <row r="421">
       <c r="A421" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B421" s="5" t="n">
@@ -15506,7 +15506,7 @@
     <row r="422">
       <c r="A422" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B422" s="5" t="n">
@@ -15521,7 +15521,7 @@
     <row r="423">
       <c r="A423" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B423" s="5" t="n">
@@ -15536,7 +15536,7 @@
     <row r="424">
       <c r="A424" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B424" s="5" t="n">
@@ -15551,7 +15551,7 @@
     <row r="425">
       <c r="A425" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B425" s="5" t="n">
@@ -15566,7 +15566,7 @@
     <row r="426">
       <c r="A426" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B426" s="5" t="n">
@@ -15581,7 +15581,7 @@
     <row r="427">
       <c r="A427" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B427" s="5" t="n">
@@ -15596,7 +15596,7 @@
     <row r="428">
       <c r="A428" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B428" s="5" t="n">
@@ -15611,7 +15611,7 @@
     <row r="429">
       <c r="A429" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B429" s="5" t="n">
@@ -15622,7 +15622,7 @@
     <row r="430">
       <c r="A430" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B430" s="5" t="n">
@@ -15630,14 +15630,14 @@
       </c>
       <c r="C430" s="5" t="inlineStr">
         <is>
-          <t># ============ 工作包2：聚类校正复算 v1（PI/S） ============</t>
+          <t># ============ 任务2：聚类校正复算 v1（PI/S） ============</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B431" s="5" t="n">
@@ -15652,7 +15652,7 @@
     <row r="432">
       <c r="A432" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B432" s="5" t="n">
@@ -15660,14 +15660,14 @@
       </c>
       <c r="C432" s="5" t="inlineStr">
         <is>
-          <t>#       效应量层处置-v1.csv、v26 工作包2 锁定参数表</t>
+          <t>#       效应量层处置-v1.csv、v26 任务2 锁定参数表</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B433" s="5" t="n">
@@ -15675,14 +15675,14 @@
       </c>
       <c r="C433" s="5" t="inlineStr">
         <is>
-          <t># 依据：聚类校正分析方案（v1，由草案冻结）、ICC来源与优先序手册-v1.md</t>
+          <t># 依据：聚类校正分析方案、ICC 来源与优先序手册</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B434" s="5" t="n">
@@ -15690,14 +15690,14 @@
       </c>
       <c r="C434" s="5" t="inlineStr">
         <is>
-          <t>WB2 = File.join(DIR, 'v26-论文质量提升五项/02-班级设计与聚类校正')</t>
+          <t>WB2 = File.join(DIR, '班级设计参数')</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B435" s="5" t="n">
@@ -15712,7 +15712,7 @@
     <row r="436">
       <c r="A436" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B436" s="5" t="n">
@@ -15723,7 +15723,7 @@
     <row r="437">
       <c r="A437" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B437" s="5" t="n">
@@ -15738,7 +15738,7 @@
     <row r="438">
       <c r="A438" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B438" s="5" t="n">
@@ -15753,7 +15753,7 @@
     <row r="439">
       <c r="A439" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B439" s="5" t="n">
@@ -15768,7 +15768,7 @@
     <row r="440">
       <c r="A440" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B440" s="5" t="n">
@@ -15783,7 +15783,7 @@
     <row r="441">
       <c r="A441" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B441" s="5" t="n">
@@ -15794,7 +15794,7 @@
     <row r="442">
       <c r="A442" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B442" s="5" t="n">
@@ -15809,7 +15809,7 @@
     <row r="443">
       <c r="A443" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B443" s="5" t="n">
@@ -15824,7 +15824,7 @@
     <row r="444">
       <c r="A444" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B444" s="5" t="n">
@@ -15839,7 +15839,7 @@
     <row r="445">
       <c r="A445" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B445" s="5" t="n">
@@ -15854,7 +15854,7 @@
     <row r="446">
       <c r="A446" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B446" s="5" t="n">
@@ -15869,7 +15869,7 @@
     <row r="447">
       <c r="A447" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B447" s="5" t="n">
@@ -15884,7 +15884,7 @@
     <row r="448">
       <c r="A448" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B448" s="5" t="n">
@@ -15899,7 +15899,7 @@
     <row r="449">
       <c r="A449" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B449" s="5" t="n">
@@ -15914,7 +15914,7 @@
     <row r="450">
       <c r="A450" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B450" s="5" t="n">
@@ -15929,7 +15929,7 @@
     <row r="451">
       <c r="A451" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B451" s="5" t="n">
@@ -15944,7 +15944,7 @@
     <row r="452">
       <c r="A452" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B452" s="5" t="n">
@@ -15959,7 +15959,7 @@
     <row r="453">
       <c r="A453" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B453" s="5" t="n">
@@ -15974,7 +15974,7 @@
     <row r="454">
       <c r="A454" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B454" s="5" t="n">
@@ -15989,7 +15989,7 @@
     <row r="455">
       <c r="A455" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B455" s="5" t="n">
@@ -16000,7 +16000,7 @@
     <row r="456">
       <c r="A456" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B456" s="5" t="n">
@@ -16015,7 +16015,7 @@
     <row r="457">
       <c r="A457" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B457" s="5" t="n">
@@ -16030,7 +16030,7 @@
     <row r="458">
       <c r="A458" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B458" s="5" t="n">
@@ -16045,7 +16045,7 @@
     <row r="459">
       <c r="A459" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B459" s="5" t="n">
@@ -16060,7 +16060,7 @@
     <row r="460">
       <c r="A460" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B460" s="5" t="n">
@@ -16075,7 +16075,7 @@
     <row r="461">
       <c r="A461" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B461" s="5" t="n">
@@ -16090,7 +16090,7 @@
     <row r="462">
       <c r="A462" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B462" s="5" t="n">
@@ -16105,7 +16105,7 @@
     <row r="463">
       <c r="A463" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B463" s="5" t="n">
@@ -16120,7 +16120,7 @@
     <row r="464">
       <c r="A464" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B464" s="5" t="n">
@@ -16131,7 +16131,7 @@
     <row r="465">
       <c r="A465" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B465" s="5" t="n">
@@ -16146,7 +16146,7 @@
     <row r="466">
       <c r="A466" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B466" s="5" t="n">
@@ -16161,7 +16161,7 @@
     <row r="467">
       <c r="A467" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B467" s="5" t="n">
@@ -16176,7 +16176,7 @@
     <row r="468">
       <c r="A468" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B468" s="5" t="n">
@@ -16191,7 +16191,7 @@
     <row r="469">
       <c r="A469" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B469" s="5" t="n">
@@ -16206,7 +16206,7 @@
     <row r="470">
       <c r="A470" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B470" s="5" t="n">
@@ -16221,7 +16221,7 @@
     <row r="471">
       <c r="A471" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B471" s="5" t="n">
@@ -16236,7 +16236,7 @@
     <row r="472">
       <c r="A472" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B472" s="5" t="n">
@@ -16251,7 +16251,7 @@
     <row r="473">
       <c r="A473" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B473" s="5" t="n">
@@ -16266,7 +16266,7 @@
     <row r="474">
       <c r="A474" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B474" s="5" t="n">
@@ -16281,7 +16281,7 @@
     <row r="475">
       <c r="A475" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B475" s="5" t="n">
@@ -16296,7 +16296,7 @@
     <row r="476">
       <c r="A476" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B476" s="5" t="n">
@@ -16311,7 +16311,7 @@
     <row r="477">
       <c r="A477" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B477" s="5" t="n">
@@ -16322,7 +16322,7 @@
     <row r="478">
       <c r="A478" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B478" s="5" t="n">
@@ -16337,7 +16337,7 @@
     <row r="479">
       <c r="A479" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B479" s="5" t="n">
@@ -16352,7 +16352,7 @@
     <row r="480">
       <c r="A480" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B480" s="5" t="n">
@@ -16363,7 +16363,7 @@
     <row r="481">
       <c r="A481" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B481" s="5" t="n">
@@ -16378,7 +16378,7 @@
     <row r="482">
       <c r="A482" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B482" s="5" t="n">
@@ -16393,7 +16393,7 @@
     <row r="483">
       <c r="A483" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B483" s="5" t="n">
@@ -16408,7 +16408,7 @@
     <row r="484">
       <c r="A484" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B484" s="5" t="n">
@@ -16423,7 +16423,7 @@
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B485" s="5" t="n">
@@ -16438,7 +16438,7 @@
     <row r="486">
       <c r="A486" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B486" s="5" t="n">
@@ -16453,7 +16453,7 @@
     <row r="487">
       <c r="A487" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B487" s="5" t="n">
@@ -16464,7 +16464,7 @@
     <row r="488">
       <c r="A488" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B488" s="5" t="n">
@@ -16479,7 +16479,7 @@
     <row r="489">
       <c r="A489" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B489" s="5" t="n">
@@ -16494,7 +16494,7 @@
     <row r="490">
       <c r="A490" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B490" s="5" t="n">
@@ -16502,14 +16502,14 @@
       </c>
       <c r="C490" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    '乙口径（22 条／9 研究，含 WP3 重判）' =&gt; sub(base, '乙'),</t>
+          <t xml:space="preserve">    '乙口径（22 条／9 研究，含 重判后）' =&gt; sub(base, '乙'),</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B491" s="5" t="n">
@@ -16517,14 +16517,14 @@
       </c>
       <c r="C491" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    '丙口径（35 条／12 研究，含 WP3 重判）' =&gt; sub(base, '丙') }</t>
+          <t xml:space="preserve">    '丙口径（35 条／12 研究，含 重判后）' =&gt; sub(base, '丙') }</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B492" s="5" t="n">
@@ -16539,7 +16539,7 @@
     <row r="493">
       <c r="A493" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B493" s="5" t="n">
@@ -16550,7 +16550,7 @@
     <row r="494">
       <c r="A494" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B494" s="5" t="n">
@@ -16558,14 +16558,14 @@
       </c>
       <c r="C494" s="5" t="inlineStr">
         <is>
-          <t>puts '聚类校正复算 v3（三级 REML；叠加工作包3 主口径重判 ＋ 补录研究35 参数记录 P-35-BING-01）'</t>
+          <t>puts '聚类校正复算 v3（三级 REML；叠加任务3 主口径重判 ＋ 补录研究35 参数记录 P-35-BING-01）'</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B495" s="5" t="n">
@@ -16580,7 +16580,7 @@
     <row r="496">
       <c r="A496" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B496" s="5" t="n">
@@ -16595,7 +16595,7 @@
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B497" s="5" t="n">
@@ -16610,7 +16610,7 @@
     <row r="498">
       <c r="A498" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B498" s="5" t="n">
@@ -16625,7 +16625,7 @@
     <row r="499">
       <c r="A499" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B499" s="5" t="n">
@@ -16640,7 +16640,7 @@
     <row r="500">
       <c r="A500" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B500" s="5" t="n">
@@ -16655,7 +16655,7 @@
     <row r="501">
       <c r="A501" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
@@ -16670,7 +16670,7 @@
     <row r="502">
       <c r="A502" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B502" s="5" t="n">
@@ -16685,7 +16685,7 @@
     <row r="503">
       <c r="A503" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -16700,7 +16700,7 @@
     <row r="504">
       <c r="A504" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B504" s="5" t="n">
@@ -16715,7 +16715,7 @@
     <row r="505">
       <c r="A505" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -16726,7 +16726,7 @@
     <row r="506">
       <c r="A506" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B506" s="5" t="n">
@@ -16741,7 +16741,7 @@
     <row r="507">
       <c r="A507" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
@@ -16756,7 +16756,7 @@
     <row r="508">
       <c r="A508" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B508" s="5" t="n">
@@ -16764,14 +16764,14 @@
       </c>
       <c r="C508" s="5" t="inlineStr">
         <is>
-          <t>puts "\n覆盖情况：工作包2 记录中共 #{REC.size} 个效应ID；其中群层分配且 m 可得者 #{n_cluster} 个（校正仅作用于这批）；"</t>
+          <t>puts "\n覆盖情况：任务2 记录中共 #{REC.size} 个效应ID；其中群层分配且 m 可得者 #{n_cluster} 个（校正仅作用于这批）；"</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="5" t="inlineStr">
         <is>
-          <t>聚类校正复算-v3.rb</t>
+          <t>聚类校正复算.rb</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
@@ -16786,7 +16786,7 @@
     <row r="510">
       <c r="A510" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B510" s="5" t="n">
@@ -16801,7 +16801,7 @@
     <row r="511">
       <c r="A511" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
@@ -16816,7 +16816,7 @@
     <row r="512">
       <c r="A512" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B512" s="5" t="n">
@@ -16831,7 +16831,7 @@
     <row r="513">
       <c r="A513" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
@@ -16846,7 +16846,7 @@
     <row r="514">
       <c r="A514" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B514" s="5" t="n">
@@ -16861,7 +16861,7 @@
     <row r="515">
       <c r="A515" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
@@ -16876,7 +16876,7 @@
     <row r="516">
       <c r="A516" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B516" s="5" t="n">
@@ -16891,7 +16891,7 @@
     <row r="517">
       <c r="A517" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
@@ -16902,7 +16902,7 @@
     <row r="518">
       <c r="A518" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B518" s="5" t="n">
@@ -16917,7 +16917,7 @@
     <row r="519">
       <c r="A519" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
@@ -16932,7 +16932,7 @@
     <row r="520">
       <c r="A520" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B520" s="5" t="n">
@@ -16947,7 +16947,7 @@
     <row r="521">
       <c r="A521" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
@@ -16958,7 +16958,7 @@
     <row r="522">
       <c r="A522" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B522" s="5" t="n">
@@ -16973,7 +16973,7 @@
     <row r="523">
       <c r="A523" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
@@ -16988,7 +16988,7 @@
     <row r="524">
       <c r="A524" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B524" s="5" t="n">
@@ -17003,7 +17003,7 @@
     <row r="525">
       <c r="A525" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
@@ -17018,7 +17018,7 @@
     <row r="526">
       <c r="A526" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B526" s="5" t="n">
@@ -17033,7 +17033,7 @@
     <row r="527">
       <c r="A527" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
@@ -17048,7 +17048,7 @@
     <row r="528">
       <c r="A528" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B528" s="5" t="n">
@@ -17063,7 +17063,7 @@
     <row r="529">
       <c r="A529" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
@@ -17078,7 +17078,7 @@
     <row r="530">
       <c r="A530" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B530" s="5" t="n">
@@ -17093,7 +17093,7 @@
     <row r="531">
       <c r="A531" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
@@ -17108,7 +17108,7 @@
     <row r="532">
       <c r="A532" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
@@ -17119,7 +17119,7 @@
     <row r="533">
       <c r="A533" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -17134,7 +17134,7 @@
     <row r="534">
       <c r="A534" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B534" s="5" t="n">
@@ -17149,7 +17149,7 @@
     <row r="535">
       <c r="A535" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
@@ -17164,7 +17164,7 @@
     <row r="536">
       <c r="A536" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B536" s="5" t="n">
@@ -17175,7 +17175,7 @@
     <row r="537">
       <c r="A537" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
@@ -17190,7 +17190,7 @@
     <row r="538">
       <c r="A538" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B538" s="5" t="n">
@@ -17205,7 +17205,7 @@
     <row r="539">
       <c r="A539" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
@@ -17220,7 +17220,7 @@
     <row r="540">
       <c r="A540" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B540" s="5" t="n">
@@ -17235,7 +17235,7 @@
     <row r="541">
       <c r="A541" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
@@ -17250,7 +17250,7 @@
     <row r="542">
       <c r="A542" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B542" s="5" t="n">
@@ -17265,7 +17265,7 @@
     <row r="543">
       <c r="A543" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B543" s="5" t="n">
@@ -17280,7 +17280,7 @@
     <row r="544">
       <c r="A544" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B544" s="5" t="n">
@@ -17291,7 +17291,7 @@
     <row r="545">
       <c r="A545" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
@@ -17306,7 +17306,7 @@
     <row r="546">
       <c r="A546" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B546" s="5" t="n">
@@ -17321,7 +17321,7 @@
     <row r="547">
       <c r="A547" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
@@ -17336,7 +17336,7 @@
     <row r="548">
       <c r="A548" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B548" s="5" t="n">
@@ -17351,7 +17351,7 @@
     <row r="549">
       <c r="A549" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
@@ -17366,7 +17366,7 @@
     <row r="550">
       <c r="A550" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B550" s="5" t="n">
@@ -17381,7 +17381,7 @@
     <row r="551">
       <c r="A551" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
@@ -17396,7 +17396,7 @@
     <row r="552">
       <c r="A552" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B552" s="5" t="n">
@@ -17411,7 +17411,7 @@
     <row r="553">
       <c r="A553" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
@@ -17426,7 +17426,7 @@
     <row r="554">
       <c r="A554" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B554" s="5" t="n">
@@ -17441,7 +17441,7 @@
     <row r="555">
       <c r="A555" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
@@ -17452,7 +17452,7 @@
     <row r="556">
       <c r="A556" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B556" s="5" t="n">
@@ -17467,7 +17467,7 @@
     <row r="557">
       <c r="A557" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
@@ -17482,7 +17482,7 @@
     <row r="558">
       <c r="A558" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B558" s="5" t="n">
@@ -17497,7 +17497,7 @@
     <row r="559">
       <c r="A559" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
@@ -17512,7 +17512,7 @@
     <row r="560">
       <c r="A560" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B560" s="5" t="n">
@@ -17527,7 +17527,7 @@
     <row r="561">
       <c r="A561" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
@@ -17542,7 +17542,7 @@
     <row r="562">
       <c r="A562" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B562" s="5" t="n">
@@ -17557,7 +17557,7 @@
     <row r="563">
       <c r="A563" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
@@ -17572,7 +17572,7 @@
     <row r="564">
       <c r="A564" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B564" s="5" t="n">
@@ -17587,7 +17587,7 @@
     <row r="565">
       <c r="A565" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
@@ -17602,7 +17602,7 @@
     <row r="566">
       <c r="A566" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B566" s="5" t="n">
@@ -17617,7 +17617,7 @@
     <row r="567">
       <c r="A567" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
@@ -17632,7 +17632,7 @@
     <row r="568">
       <c r="A568" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B568" s="5" t="n">
@@ -17647,7 +17647,7 @@
     <row r="569">
       <c r="A569" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
@@ -17662,7 +17662,7 @@
     <row r="570">
       <c r="A570" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B570" s="5" t="n">
@@ -17677,7 +17677,7 @@
     <row r="571">
       <c r="A571" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -17688,7 +17688,7 @@
     <row r="572">
       <c r="A572" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B572" s="5" t="n">
@@ -17703,7 +17703,7 @@
     <row r="573">
       <c r="A573" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -17718,7 +17718,7 @@
     <row r="574">
       <c r="A574" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B574" s="5" t="n">
@@ -17733,7 +17733,7 @@
     <row r="575">
       <c r="A575" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
@@ -17748,7 +17748,7 @@
     <row r="576">
       <c r="A576" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B576" s="5" t="n">
@@ -17763,7 +17763,7 @@
     <row r="577">
       <c r="A577" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
@@ -17778,7 +17778,7 @@
     <row r="578">
       <c r="A578" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
@@ -17793,7 +17793,7 @@
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
@@ -17804,7 +17804,7 @@
     <row r="580">
       <c r="A580" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
@@ -17819,7 +17819,7 @@
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -17834,7 +17834,7 @@
     <row r="582">
       <c r="A582" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
@@ -17849,7 +17849,7 @@
     <row r="583">
       <c r="A583" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -17864,7 +17864,7 @@
     <row r="584">
       <c r="A584" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
@@ -17879,7 +17879,7 @@
     <row r="585">
       <c r="A585" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -17894,7 +17894,7 @@
     <row r="586">
       <c r="A586" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
@@ -17909,7 +17909,7 @@
     <row r="587">
       <c r="A587" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -17924,7 +17924,7 @@
     <row r="588">
       <c r="A588" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
@@ -17939,7 +17939,7 @@
     <row r="589">
       <c r="A589" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -17954,7 +17954,7 @@
     <row r="590">
       <c r="A590" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
@@ -17969,7 +17969,7 @@
     <row r="591">
       <c r="A591" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -17984,7 +17984,7 @@
     <row r="592">
       <c r="A592" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
@@ -17999,7 +17999,7 @@
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
@@ -18014,7 +18014,7 @@
     <row r="594">
       <c r="A594" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B594" s="5" t="n">
@@ -18029,7 +18029,7 @@
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B595" s="5" t="n">
@@ -18044,7 +18044,7 @@
     <row r="596">
       <c r="A596" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
@@ -18059,7 +18059,7 @@
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B597" s="5" t="n">
@@ -18074,7 +18074,7 @@
     <row r="598">
       <c r="A598" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B598" s="5" t="n">
@@ -18089,7 +18089,7 @@
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
@@ -18104,7 +18104,7 @@
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
@@ -18119,7 +18119,7 @@
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
@@ -18134,7 +18134,7 @@
     <row r="602">
       <c r="A602" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
@@ -18149,7 +18149,7 @@
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
@@ -18164,7 +18164,7 @@
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
@@ -18179,7 +18179,7 @@
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B605" s="5" t="n">
@@ -18194,7 +18194,7 @@
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
@@ -18209,7 +18209,7 @@
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
@@ -18224,7 +18224,7 @@
     <row r="608">
       <c r="A608" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
@@ -18239,7 +18239,7 @@
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
@@ -18254,7 +18254,7 @@
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
@@ -18269,7 +18269,7 @@
     <row r="611">
       <c r="A611" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B611" s="5" t="n">
@@ -18284,7 +18284,7 @@
     <row r="612">
       <c r="A612" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B612" s="5" t="n">
@@ -18299,7 +18299,7 @@
     <row r="613">
       <c r="A613" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
@@ -18310,7 +18310,7 @@
     <row r="614">
       <c r="A614" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B614" s="5" t="n">
@@ -18325,7 +18325,7 @@
     <row r="615">
       <c r="A615" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
@@ -18340,7 +18340,7 @@
     <row r="616">
       <c r="A616" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B616" s="5" t="n">
@@ -18355,7 +18355,7 @@
     <row r="617">
       <c r="A617" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B617" s="5" t="n">
@@ -18370,7 +18370,7 @@
     <row r="618">
       <c r="A618" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B618" s="5" t="n">
@@ -18385,7 +18385,7 @@
     <row r="619">
       <c r="A619" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B619" s="5" t="n">
@@ -18400,7 +18400,7 @@
     <row r="620">
       <c r="A620" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B620" s="5" t="n">
@@ -18415,7 +18415,7 @@
     <row r="621">
       <c r="A621" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B621" s="5" t="n">
@@ -18430,7 +18430,7 @@
     <row r="622">
       <c r="A622" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B622" s="5" t="n">
@@ -18445,7 +18445,7 @@
     <row r="623">
       <c r="A623" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B623" s="5" t="n">
@@ -18460,7 +18460,7 @@
     <row r="624">
       <c r="A624" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B624" s="5" t="n">
@@ -18475,7 +18475,7 @@
     <row r="625">
       <c r="A625" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B625" s="5" t="n">
@@ -18490,7 +18490,7 @@
     <row r="626">
       <c r="A626" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B626" s="5" t="n">
@@ -18505,7 +18505,7 @@
     <row r="627">
       <c r="A627" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B627" s="5" t="n">
@@ -18520,7 +18520,7 @@
     <row r="628">
       <c r="A628" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B628" s="5" t="n">
@@ -18535,7 +18535,7 @@
     <row r="629">
       <c r="A629" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B629" s="5" t="n">
@@ -18550,7 +18550,7 @@
     <row r="630">
       <c r="A630" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B630" s="5" t="n">
@@ -18565,7 +18565,7 @@
     <row r="631">
       <c r="A631" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B631" s="5" t="n">
@@ -18580,7 +18580,7 @@
     <row r="632">
       <c r="A632" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B632" s="5" t="n">
@@ -18595,7 +18595,7 @@
     <row r="633">
       <c r="A633" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B633" s="5" t="n">
@@ -18610,7 +18610,7 @@
     <row r="634">
       <c r="A634" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B634" s="5" t="n">
@@ -18625,7 +18625,7 @@
     <row r="635">
       <c r="A635" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B635" s="5" t="n">
@@ -18640,7 +18640,7 @@
     <row r="636">
       <c r="A636" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B636" s="5" t="n">
@@ -18655,7 +18655,7 @@
     <row r="637">
       <c r="A637" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B637" s="5" t="n">
@@ -18670,7 +18670,7 @@
     <row r="638">
       <c r="A638" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B638" s="5" t="n">
@@ -18685,7 +18685,7 @@
     <row r="639">
       <c r="A639" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B639" s="5" t="n">
@@ -18700,7 +18700,7 @@
     <row r="640">
       <c r="A640" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B640" s="5" t="n">
@@ -18715,7 +18715,7 @@
     <row r="641">
       <c r="A641" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B641" s="5" t="n">
@@ -18730,7 +18730,7 @@
     <row r="642">
       <c r="A642" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B642" s="5" t="n">
@@ -18745,7 +18745,7 @@
     <row r="643">
       <c r="A643" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B643" s="5" t="n">
@@ -18760,7 +18760,7 @@
     <row r="644">
       <c r="A644" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B644" s="5" t="n">
@@ -18775,7 +18775,7 @@
     <row r="645">
       <c r="A645" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B645" s="5" t="n">
@@ -18790,7 +18790,7 @@
     <row r="646">
       <c r="A646" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B646" s="5" t="n">
@@ -18805,7 +18805,7 @@
     <row r="647">
       <c r="A647" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B647" s="5" t="n">
@@ -18820,7 +18820,7 @@
     <row r="648">
       <c r="A648" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B648" s="5" t="n">
@@ -18835,7 +18835,7 @@
     <row r="649">
       <c r="A649" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B649" s="5" t="n">
@@ -18850,7 +18850,7 @@
     <row r="650">
       <c r="A650" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B650" s="5" t="n">
@@ -18865,7 +18865,7 @@
     <row r="651">
       <c r="A651" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B651" s="5" t="n">
@@ -18880,7 +18880,7 @@
     <row r="652">
       <c r="A652" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B652" s="5" t="n">
@@ -18895,7 +18895,7 @@
     <row r="653">
       <c r="A653" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B653" s="5" t="n">
@@ -18910,7 +18910,7 @@
     <row r="654">
       <c r="A654" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B654" s="5" t="n">
@@ -18925,7 +18925,7 @@
     <row r="655">
       <c r="A655" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B655" s="5" t="n">
@@ -18940,7 +18940,7 @@
     <row r="656">
       <c r="A656" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B656" s="5" t="n">
@@ -18955,7 +18955,7 @@
     <row r="657">
       <c r="A657" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B657" s="5" t="n">
@@ -18970,7 +18970,7 @@
     <row r="658">
       <c r="A658" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B658" s="5" t="n">
@@ -18985,7 +18985,7 @@
     <row r="659">
       <c r="A659" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B659" s="5" t="n">
@@ -19000,7 +19000,7 @@
     <row r="660">
       <c r="A660" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B660" s="5" t="n">
@@ -19015,7 +19015,7 @@
     <row r="661">
       <c r="A661" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B661" s="5" t="n">
@@ -19030,7 +19030,7 @@
     <row r="662">
       <c r="A662" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B662" s="5" t="n">
@@ -19045,7 +19045,7 @@
     <row r="663">
       <c r="A663" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B663" s="5" t="n">
@@ -19060,7 +19060,7 @@
     <row r="664">
       <c r="A664" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B664" s="5" t="n">
@@ -19075,7 +19075,7 @@
     <row r="665">
       <c r="A665" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B665" s="5" t="n">
@@ -19090,7 +19090,7 @@
     <row r="666">
       <c r="A666" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B666" s="5" t="n">
@@ -19105,7 +19105,7 @@
     <row r="667">
       <c r="A667" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B667" s="5" t="n">
@@ -19120,7 +19120,7 @@
     <row r="668">
       <c r="A668" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B668" s="5" t="n">
@@ -19135,7 +19135,7 @@
     <row r="669">
       <c r="A669" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B669" s="5" t="n">
@@ -19150,7 +19150,7 @@
     <row r="670">
       <c r="A670" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B670" s="5" t="n">
@@ -19165,7 +19165,7 @@
     <row r="671">
       <c r="A671" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B671" s="5" t="n">
@@ -19180,7 +19180,7 @@
     <row r="672">
       <c r="A672" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B672" s="5" t="n">
@@ -19195,7 +19195,7 @@
     <row r="673">
       <c r="A673" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B673" s="5" t="n">
@@ -19210,7 +19210,7 @@
     <row r="674">
       <c r="A674" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B674" s="5" t="n">
@@ -19225,7 +19225,7 @@
     <row r="675">
       <c r="A675" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B675" s="5" t="n">
@@ -19240,7 +19240,7 @@
     <row r="676">
       <c r="A676" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B676" s="5" t="n">
@@ -19251,7 +19251,7 @@
     <row r="677">
       <c r="A677" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B677" s="5" t="n">
@@ -19266,7 +19266,7 @@
     <row r="678">
       <c r="A678" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B678" s="5" t="n">
@@ -19281,7 +19281,7 @@
     <row r="679">
       <c r="A679" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B679" s="5" t="n">
@@ -19296,7 +19296,7 @@
     <row r="680">
       <c r="A680" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B680" s="5" t="n">
@@ -19311,7 +19311,7 @@
     <row r="681">
       <c r="A681" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B681" s="5" t="n">
@@ -19326,7 +19326,7 @@
     <row r="682">
       <c r="A682" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B682" s="5" t="n">
@@ -19337,7 +19337,7 @@
     <row r="683">
       <c r="A683" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B683" s="5" t="n">
@@ -19352,7 +19352,7 @@
     <row r="684">
       <c r="A684" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B684" s="5" t="n">
@@ -19367,7 +19367,7 @@
     <row r="685">
       <c r="A685" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B685" s="5" t="n">
@@ -19382,7 +19382,7 @@
     <row r="686">
       <c r="A686" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B686" s="5" t="n">
@@ -19397,7 +19397,7 @@
     <row r="687">
       <c r="A687" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B687" s="5" t="n">
@@ -19412,7 +19412,7 @@
     <row r="688">
       <c r="A688" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B688" s="5" t="n">
@@ -19427,7 +19427,7 @@
     <row r="689">
       <c r="A689" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B689" s="5" t="n">
@@ -19438,7 +19438,7 @@
     <row r="690">
       <c r="A690" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B690" s="5" t="n">
@@ -19453,7 +19453,7 @@
     <row r="691">
       <c r="A691" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B691" s="5" t="n">
@@ -19468,7 +19468,7 @@
     <row r="692">
       <c r="A692" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B692" s="5" t="n">
@@ -19483,7 +19483,7 @@
     <row r="693">
       <c r="A693" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B693" s="5" t="n">
@@ -19498,7 +19498,7 @@
     <row r="694">
       <c r="A694" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B694" s="5" t="n">
@@ -19513,7 +19513,7 @@
     <row r="695">
       <c r="A695" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B695" s="5" t="n">
@@ -19528,7 +19528,7 @@
     <row r="696">
       <c r="A696" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B696" s="5" t="n">
@@ -19543,7 +19543,7 @@
     <row r="697">
       <c r="A697" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B697" s="5" t="n">
@@ -19558,7 +19558,7 @@
     <row r="698">
       <c r="A698" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B698" s="5" t="n">
@@ -19573,7 +19573,7 @@
     <row r="699">
       <c r="A699" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B699" s="5" t="n">
@@ -19584,7 +19584,7 @@
     <row r="700">
       <c r="A700" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B700" s="5" t="n">
@@ -19599,7 +19599,7 @@
     <row r="701">
       <c r="A701" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B701" s="5" t="n">
@@ -19614,7 +19614,7 @@
     <row r="702">
       <c r="A702" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B702" s="5" t="n">
@@ -19629,7 +19629,7 @@
     <row r="703">
       <c r="A703" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B703" s="5" t="n">
@@ -19644,7 +19644,7 @@
     <row r="704">
       <c r="A704" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B704" s="5" t="n">
@@ -19659,7 +19659,7 @@
     <row r="705">
       <c r="A705" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B705" s="5" t="n">
@@ -19674,7 +19674,7 @@
     <row r="706">
       <c r="A706" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B706" s="5" t="n">
@@ -19689,7 +19689,7 @@
     <row r="707">
       <c r="A707" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B707" s="5" t="n">
@@ -19704,7 +19704,7 @@
     <row r="708">
       <c r="A708" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B708" s="5" t="n">
@@ -19719,7 +19719,7 @@
     <row r="709">
       <c r="A709" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B709" s="5" t="n">
@@ -19734,7 +19734,7 @@
     <row r="710">
       <c r="A710" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B710" s="5" t="n">
@@ -19749,7 +19749,7 @@
     <row r="711">
       <c r="A711" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B711" s="5" t="n">
@@ -19764,7 +19764,7 @@
     <row r="712">
       <c r="A712" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B712" s="5" t="n">
@@ -19779,7 +19779,7 @@
     <row r="713">
       <c r="A713" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B713" s="5" t="n">
@@ -19794,7 +19794,7 @@
     <row r="714">
       <c r="A714" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B714" s="5" t="n">
@@ -19809,7 +19809,7 @@
     <row r="715">
       <c r="A715" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B715" s="5" t="n">
@@ -19824,7 +19824,7 @@
     <row r="716">
       <c r="A716" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B716" s="5" t="n">
@@ -19839,7 +19839,7 @@
     <row r="717">
       <c r="A717" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B717" s="5" t="n">
@@ -19854,7 +19854,7 @@
     <row r="718">
       <c r="A718" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B718" s="5" t="n">
@@ -19869,7 +19869,7 @@
     <row r="719">
       <c r="A719" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B719" s="5" t="n">
@@ -19884,7 +19884,7 @@
     <row r="720">
       <c r="A720" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B720" s="5" t="n">
@@ -19895,7 +19895,7 @@
     <row r="721">
       <c r="A721" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B721" s="5" t="n">
@@ -19910,7 +19910,7 @@
     <row r="722">
       <c r="A722" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B722" s="5" t="n">
@@ -19925,7 +19925,7 @@
     <row r="723">
       <c r="A723" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B723" s="5" t="n">
@@ -19940,7 +19940,7 @@
     <row r="724">
       <c r="A724" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B724" s="5" t="n">
@@ -19955,7 +19955,7 @@
     <row r="725">
       <c r="A725" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B725" s="5" t="n">
@@ -19970,7 +19970,7 @@
     <row r="726">
       <c r="A726" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B726" s="5" t="n">
@@ -19985,7 +19985,7 @@
     <row r="727">
       <c r="A727" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B727" s="5" t="n">
@@ -20000,7 +20000,7 @@
     <row r="728">
       <c r="A728" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B728" s="5" t="n">
@@ -20015,7 +20015,7 @@
     <row r="729">
       <c r="A729" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B729" s="5" t="n">
@@ -20030,7 +20030,7 @@
     <row r="730">
       <c r="A730" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B730" s="5" t="n">
@@ -20041,7 +20041,7 @@
     <row r="731">
       <c r="A731" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B731" s="5" t="n">
@@ -20056,7 +20056,7 @@
     <row r="732">
       <c r="A732" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B732" s="5" t="n">
@@ -20071,7 +20071,7 @@
     <row r="733">
       <c r="A733" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B733" s="5" t="n">
@@ -20086,7 +20086,7 @@
     <row r="734">
       <c r="A734" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B734" s="5" t="n">
@@ -20101,7 +20101,7 @@
     <row r="735">
       <c r="A735" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B735" s="5" t="n">
@@ -20116,7 +20116,7 @@
     <row r="736">
       <c r="A736" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B736" s="5" t="n">
@@ -20131,7 +20131,7 @@
     <row r="737">
       <c r="A737" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B737" s="5" t="n">
@@ -20146,7 +20146,7 @@
     <row r="738">
       <c r="A738" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B738" s="5" t="n">
@@ -20161,7 +20161,7 @@
     <row r="739">
       <c r="A739" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B739" s="5" t="n">
@@ -20176,7 +20176,7 @@
     <row r="740">
       <c r="A740" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B740" s="5" t="n">
@@ -20191,7 +20191,7 @@
     <row r="741">
       <c r="A741" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B741" s="5" t="n">
@@ -20206,7 +20206,7 @@
     <row r="742">
       <c r="A742" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B742" s="5" t="n">
@@ -20217,7 +20217,7 @@
     <row r="743">
       <c r="A743" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B743" s="5" t="n">
@@ -20232,7 +20232,7 @@
     <row r="744">
       <c r="A744" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B744" s="5" t="n">
@@ -20247,7 +20247,7 @@
     <row r="745">
       <c r="A745" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B745" s="5" t="n">
@@ -20262,7 +20262,7 @@
     <row r="746">
       <c r="A746" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B746" s="5" t="n">
@@ -20277,7 +20277,7 @@
     <row r="747">
       <c r="A747" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B747" s="5" t="n">
@@ -20292,7 +20292,7 @@
     <row r="748">
       <c r="A748" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B748" s="5" t="n">
@@ -20307,7 +20307,7 @@
     <row r="749">
       <c r="A749" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B749" s="5" t="n">
@@ -20322,7 +20322,7 @@
     <row r="750">
       <c r="A750" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B750" s="5" t="n">
@@ -20337,7 +20337,7 @@
     <row r="751">
       <c r="A751" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B751" s="5" t="n">
@@ -20352,7 +20352,7 @@
     <row r="752">
       <c r="A752" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B752" s="5" t="n">
@@ -20367,7 +20367,7 @@
     <row r="753">
       <c r="A753" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B753" s="5" t="n">
@@ -20382,7 +20382,7 @@
     <row r="754">
       <c r="A754" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B754" s="5" t="n">
@@ -20397,7 +20397,7 @@
     <row r="755">
       <c r="A755" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B755" s="5" t="n">
@@ -20412,7 +20412,7 @@
     <row r="756">
       <c r="A756" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B756" s="5" t="n">
@@ -20427,7 +20427,7 @@
     <row r="757">
       <c r="A757" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B757" s="5" t="n">
@@ -20442,7 +20442,7 @@
     <row r="758">
       <c r="A758" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B758" s="5" t="n">
@@ -20457,7 +20457,7 @@
     <row r="759">
       <c r="A759" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B759" s="5" t="n">
@@ -20472,7 +20472,7 @@
     <row r="760">
       <c r="A760" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B760" s="5" t="n">
@@ -20487,7 +20487,7 @@
     <row r="761">
       <c r="A761" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B761" s="5" t="n">
@@ -20502,7 +20502,7 @@
     <row r="762">
       <c r="A762" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B762" s="5" t="n">
@@ -20517,7 +20517,7 @@
     <row r="763">
       <c r="A763" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B763" s="5" t="n">
@@ -20532,7 +20532,7 @@
     <row r="764">
       <c r="A764" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B764" s="5" t="n">
@@ -20547,7 +20547,7 @@
     <row r="765">
       <c r="A765" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B765" s="5" t="n">
@@ -20562,7 +20562,7 @@
     <row r="766">
       <c r="A766" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B766" s="5" t="n">
@@ -20577,7 +20577,7 @@
     <row r="767">
       <c r="A767" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B767" s="5" t="n">
@@ -20588,7 +20588,7 @@
     <row r="768">
       <c r="A768" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B768" s="5" t="n">
@@ -20603,7 +20603,7 @@
     <row r="769">
       <c r="A769" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B769" s="5" t="n">
@@ -20618,7 +20618,7 @@
     <row r="770">
       <c r="A770" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B770" s="5" t="n">
@@ -20633,7 +20633,7 @@
     <row r="771">
       <c r="A771" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B771" s="5" t="n">
@@ -20648,7 +20648,7 @@
     <row r="772">
       <c r="A772" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B772" s="5" t="n">
@@ -20663,7 +20663,7 @@
     <row r="773">
       <c r="A773" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B773" s="5" t="n">
@@ -20678,7 +20678,7 @@
     <row r="774">
       <c r="A774" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B774" s="5" t="n">
@@ -20693,7 +20693,7 @@
     <row r="775">
       <c r="A775" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B775" s="5" t="n">
@@ -20708,7 +20708,7 @@
     <row r="776">
       <c r="A776" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B776" s="5" t="n">
@@ -20723,7 +20723,7 @@
     <row r="777">
       <c r="A777" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B777" s="5" t="n">
@@ -20738,7 +20738,7 @@
     <row r="778">
       <c r="A778" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B778" s="5" t="n">
@@ -20753,7 +20753,7 @@
     <row r="779">
       <c r="A779" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B779" s="5" t="n">
@@ -20764,7 +20764,7 @@
     <row r="780">
       <c r="A780" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B780" s="5" t="n">
@@ -20779,7 +20779,7 @@
     <row r="781">
       <c r="A781" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B781" s="5" t="n">
@@ -20794,7 +20794,7 @@
     <row r="782">
       <c r="A782" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B782" s="5" t="n">
@@ -20809,7 +20809,7 @@
     <row r="783">
       <c r="A783" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B783" s="5" t="n">
@@ -20824,7 +20824,7 @@
     <row r="784">
       <c r="A784" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B784" s="5" t="n">
@@ -20839,7 +20839,7 @@
     <row r="785">
       <c r="A785" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B785" s="5" t="n">
@@ -20854,7 +20854,7 @@
     <row r="786">
       <c r="A786" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B786" s="5" t="n">
@@ -20869,7 +20869,7 @@
     <row r="787">
       <c r="A787" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B787" s="5" t="n">
@@ -20884,7 +20884,7 @@
     <row r="788">
       <c r="A788" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B788" s="5" t="n">
@@ -20899,7 +20899,7 @@
     <row r="789">
       <c r="A789" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B789" s="5" t="n">
@@ -20914,7 +20914,7 @@
     <row r="790">
       <c r="A790" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B790" s="5" t="n">
@@ -20929,7 +20929,7 @@
     <row r="791">
       <c r="A791" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B791" s="5" t="n">
@@ -20944,7 +20944,7 @@
     <row r="792">
       <c r="A792" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B792" s="5" t="n">
@@ -20959,7 +20959,7 @@
     <row r="793">
       <c r="A793" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B793" s="5" t="n">
@@ -20974,7 +20974,7 @@
     <row r="794">
       <c r="A794" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B794" s="5" t="n">
@@ -20989,7 +20989,7 @@
     <row r="795">
       <c r="A795" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B795" s="5" t="n">
@@ -21004,7 +21004,7 @@
     <row r="796">
       <c r="A796" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B796" s="5" t="n">
@@ -21019,7 +21019,7 @@
     <row r="797">
       <c r="A797" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B797" s="5" t="n">
@@ -21034,7 +21034,7 @@
     <row r="798">
       <c r="A798" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B798" s="5" t="n">
@@ -21049,7 +21049,7 @@
     <row r="799">
       <c r="A799" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B799" s="5" t="n">
@@ -21064,7 +21064,7 @@
     <row r="800">
       <c r="A800" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B800" s="5" t="n">
@@ -21075,7 +21075,7 @@
     <row r="801">
       <c r="A801" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B801" s="5" t="n">
@@ -21090,7 +21090,7 @@
     <row r="802">
       <c r="A802" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B802" s="5" t="n">
@@ -21105,7 +21105,7 @@
     <row r="803">
       <c r="A803" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B803" s="5" t="n">
@@ -21120,7 +21120,7 @@
     <row r="804">
       <c r="A804" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B804" s="5" t="n">
@@ -21135,7 +21135,7 @@
     <row r="805">
       <c r="A805" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B805" s="5" t="n">
@@ -21150,7 +21150,7 @@
     <row r="806">
       <c r="A806" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B806" s="5" t="n">
@@ -21165,7 +21165,7 @@
     <row r="807">
       <c r="A807" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B807" s="5" t="n">
@@ -21180,7 +21180,7 @@
     <row r="808">
       <c r="A808" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B808" s="5" t="n">
@@ -21195,7 +21195,7 @@
     <row r="809">
       <c r="A809" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B809" s="5" t="n">
@@ -21210,7 +21210,7 @@
     <row r="810">
       <c r="A810" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B810" s="5" t="n">
@@ -21225,7 +21225,7 @@
     <row r="811">
       <c r="A811" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B811" s="5" t="n">
@@ -21240,7 +21240,7 @@
     <row r="812">
       <c r="A812" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B812" s="5" t="n">
@@ -21255,7 +21255,7 @@
     <row r="813">
       <c r="A813" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B813" s="5" t="n">
@@ -21270,7 +21270,7 @@
     <row r="814">
       <c r="A814" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B814" s="5" t="n">
@@ -21285,7 +21285,7 @@
     <row r="815">
       <c r="A815" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B815" s="5" t="n">
@@ -21300,7 +21300,7 @@
     <row r="816">
       <c r="A816" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B816" s="5" t="n">
@@ -21315,7 +21315,7 @@
     <row r="817">
       <c r="A817" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B817" s="5" t="n">
@@ -21330,7 +21330,7 @@
     <row r="818">
       <c r="A818" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B818" s="5" t="n">
@@ -21345,7 +21345,7 @@
     <row r="819">
       <c r="A819" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B819" s="5" t="n">
@@ -21360,7 +21360,7 @@
     <row r="820">
       <c r="A820" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B820" s="5" t="n">
@@ -21375,7 +21375,7 @@
     <row r="821">
       <c r="A821" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B821" s="5" t="n">
@@ -21386,7 +21386,7 @@
     <row r="822">
       <c r="A822" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B822" s="5" t="n">
@@ -21401,7 +21401,7 @@
     <row r="823">
       <c r="A823" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B823" s="5" t="n">
@@ -21416,7 +21416,7 @@
     <row r="824">
       <c r="A824" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B824" s="5" t="n">
@@ -21431,7 +21431,7 @@
     <row r="825">
       <c r="A825" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B825" s="5" t="n">
@@ -21446,7 +21446,7 @@
     <row r="826">
       <c r="A826" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B826" s="5" t="n">
@@ -21461,7 +21461,7 @@
     <row r="827">
       <c r="A827" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B827" s="5" t="n">
@@ -21476,7 +21476,7 @@
     <row r="828">
       <c r="A828" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B828" s="5" t="n">
@@ -21491,7 +21491,7 @@
     <row r="829">
       <c r="A829" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B829" s="5" t="n">
@@ -21506,7 +21506,7 @@
     <row r="830">
       <c r="A830" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B830" s="5" t="n">
@@ -21521,7 +21521,7 @@
     <row r="831">
       <c r="A831" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B831" s="5" t="n">
@@ -21536,7 +21536,7 @@
     <row r="832">
       <c r="A832" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B832" s="5" t="n">
@@ -21551,7 +21551,7 @@
     <row r="833">
       <c r="A833" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B833" s="5" t="n">
@@ -21566,7 +21566,7 @@
     <row r="834">
       <c r="A834" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B834" s="5" t="n">
@@ -21577,7 +21577,7 @@
     <row r="835">
       <c r="A835" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B835" s="5" t="n">
@@ -21592,7 +21592,7 @@
     <row r="836">
       <c r="A836" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B836" s="5" t="n">
@@ -21607,7 +21607,7 @@
     <row r="837">
       <c r="A837" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B837" s="5" t="n">
@@ -21622,7 +21622,7 @@
     <row r="838">
       <c r="A838" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B838" s="5" t="n">
@@ -21637,7 +21637,7 @@
     <row r="839">
       <c r="A839" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B839" s="5" t="n">
@@ -21652,7 +21652,7 @@
     <row r="840">
       <c r="A840" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B840" s="5" t="n">
@@ -21667,7 +21667,7 @@
     <row r="841">
       <c r="A841" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B841" s="5" t="n">
@@ -21682,7 +21682,7 @@
     <row r="842">
       <c r="A842" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B842" s="5" t="n">
@@ -21697,7 +21697,7 @@
     <row r="843">
       <c r="A843" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B843" s="5" t="n">
@@ -21712,7 +21712,7 @@
     <row r="844">
       <c r="A844" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B844" s="5" t="n">
@@ -21727,7 +21727,7 @@
     <row r="845">
       <c r="A845" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B845" s="5" t="n">
@@ -21742,7 +21742,7 @@
     <row r="846">
       <c r="A846" s="5" t="inlineStr">
         <is>
-          <t>meta_analysis_v9.rb</t>
+          <t>meta_analysis.rb</t>
         </is>
       </c>
       <c r="B846" s="5" t="n">
@@ -46682,7 +46682,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>集合占位</t>
+          <t>集合</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -67040,7 +67040,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -67071,7 +67071,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>【M2】设计效应（DE）膨胀覆盖面</t>
+          <t>设计效应（DE）膨胀覆盖面</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
